--- a/modules/sheet/sheet-conformance/tests/golden/zip-container/02-formulas.edited.xlsx
+++ b/modules/sheet/sheet-conformance/tests/golden/zip-container/02-formulas.edited.xlsx
@@ -23,27 +23,23 @@
   <dimension ref="A1:F302"/>
   <sheetData>
     <row r="1">
-      <c r="A1">
+      <c r="A1" t="n">
         <v>2</v>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Sum</t>
-        </is>
+      <c r="B1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
+      <c r="A2" t="n">
         <v>3</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
+      <c r="B2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
+      <c r="A3" t="n">
         <f>SUM(A1:A2)</f>
         <v>5</v>
       </c>
